--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/130.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/130.xlsx
@@ -426,13 +426,13 @@
         <v>3.499661217556752</v>
       </c>
       <c r="E2">
-        <v>-15.11703984973811</v>
+        <v>-17.95303528362934</v>
       </c>
       <c r="F2">
-        <v>-3.185244283063986</v>
+        <v>-4.17170063448336</v>
       </c>
       <c r="G2">
-        <v>-10.15713522723684</v>
+        <v>-10.9387503859027</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>3.338075854143511</v>
       </c>
       <c r="E3">
-        <v>-16.07604957033162</v>
+        <v>-18.3250010430923</v>
       </c>
       <c r="F3">
-        <v>-3.545349675306779</v>
+        <v>-4.331248338099559</v>
       </c>
       <c r="G3">
-        <v>-9.365389074185165</v>
+        <v>-10.85576264758498</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>3.08563196711746</v>
       </c>
       <c r="E4">
-        <v>-18.43368643025174</v>
+        <v>-19.81685116381601</v>
       </c>
       <c r="F4">
-        <v>-4.322141266873182</v>
+        <v>-4.130176233315828</v>
       </c>
       <c r="G4">
-        <v>-10.40496668440975</v>
+        <v>-11.44188133515139</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>2.785766847866534</v>
       </c>
       <c r="E5">
-        <v>-18.66349191927716</v>
+        <v>-19.26731070094868</v>
       </c>
       <c r="F5">
-        <v>-3.480380819905214</v>
+        <v>-3.687367467944935</v>
       </c>
       <c r="G5">
-        <v>-10.11350707437475</v>
+        <v>-11.16177324259855</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>2.460766509242454</v>
       </c>
       <c r="E6">
-        <v>-20.9041743482901</v>
+        <v>-20.55670422922097</v>
       </c>
       <c r="F6">
-        <v>-2.854910415277808</v>
+        <v>-3.8411058309653</v>
       </c>
       <c r="G6">
-        <v>-9.414063796341882</v>
+        <v>-12.14781622961006</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>2.146652170847706</v>
       </c>
       <c r="E7">
-        <v>-22.6736500332333</v>
+        <v>-21.94903925339047</v>
       </c>
       <c r="F7">
-        <v>-3.641523959139204</v>
+        <v>-3.54201798161272</v>
       </c>
       <c r="G7">
-        <v>-9.977043454597254</v>
+        <v>-12.28655902941559</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>1.876249467539602</v>
       </c>
       <c r="E8">
-        <v>-21.37202114439807</v>
+        <v>-22.78651770419684</v>
       </c>
       <c r="F8">
-        <v>-2.892560542102448</v>
+        <v>-3.297628060234393</v>
       </c>
       <c r="G8">
-        <v>-11.35474642905069</v>
+        <v>-12.44032666434298</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>1.688431450610714</v>
       </c>
       <c r="E9">
-        <v>-24.0423325189079</v>
+        <v>-23.75934931207938</v>
       </c>
       <c r="F9">
-        <v>-2.750483107011291</v>
+        <v>-3.252299795953204</v>
       </c>
       <c r="G9">
-        <v>-10.06509473204944</v>
+        <v>-12.24286169182183</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>1.614278064604128</v>
       </c>
       <c r="E10">
-        <v>-24.35929314758484</v>
+        <v>-24.51074830496736</v>
       </c>
       <c r="F10">
-        <v>-2.976577705931388</v>
+        <v>-3.162486545406876</v>
       </c>
       <c r="G10">
-        <v>-9.499188429107425</v>
+        <v>-12.35157570734038</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>1.68476536143556</v>
       </c>
       <c r="E11">
-        <v>-24.22967972855959</v>
+        <v>-25.4599107615097</v>
       </c>
       <c r="F11">
-        <v>-2.913629238625251</v>
+        <v>-3.039368783430993</v>
       </c>
       <c r="G11">
-        <v>-8.870972790381609</v>
+        <v>-12.17431006572068</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>1.911727715243118</v>
       </c>
       <c r="E12">
-        <v>-24.74382237130542</v>
+        <v>-25.5115642507566</v>
       </c>
       <c r="F12">
-        <v>-1.993530914741936</v>
+        <v>-2.920496404394459</v>
       </c>
       <c r="G12">
-        <v>-9.510934169022844</v>
+        <v>-12.03629827440066</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>2.301283517639143</v>
       </c>
       <c r="E13">
-        <v>-27.89823621104859</v>
+        <v>-27.23813726271432</v>
       </c>
       <c r="F13">
-        <v>-1.825963786299236</v>
+        <v>-2.85643792476857</v>
       </c>
       <c r="G13">
-        <v>-9.335584813933016</v>
+        <v>-11.32982295581163</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>2.839125321345934</v>
       </c>
       <c r="E14">
-        <v>-26.10300646268013</v>
+        <v>-27.31555312180912</v>
       </c>
       <c r="F14">
-        <v>-2.380289856537206</v>
+        <v>-2.901539216381392</v>
       </c>
       <c r="G14">
-        <v>-8.050567188580988</v>
+        <v>-11.25367275757804</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>3.501921121142412</v>
       </c>
       <c r="E15">
-        <v>-27.62264987358959</v>
+        <v>-28.63568249049081</v>
       </c>
       <c r="F15">
-        <v>-2.072138011063193</v>
+        <v>-2.334863016535084</v>
       </c>
       <c r="G15">
-        <v>-8.105934554497022</v>
+        <v>-10.2659915283356</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>4.254676586133781</v>
       </c>
       <c r="E16">
-        <v>-30.86111432751899</v>
+        <v>-30.06518875601752</v>
       </c>
       <c r="F16">
-        <v>-1.769701072301093</v>
+        <v>-1.963817376003518</v>
       </c>
       <c r="G16">
-        <v>-6.894650883259511</v>
+        <v>-9.368960572785808</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>5.050873667651461</v>
       </c>
       <c r="E17">
-        <v>-28.26894354748014</v>
+        <v>-31.07492164652116</v>
       </c>
       <c r="F17">
-        <v>-1.976354716644889</v>
+        <v>-2.081335374336476</v>
       </c>
       <c r="G17">
-        <v>-4.483581259963752</v>
+        <v>-8.378714286982607</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>5.845936329370853</v>
       </c>
       <c r="E18">
-        <v>-30.47701703777619</v>
+        <v>-31.90093931067667</v>
       </c>
       <c r="F18">
-        <v>-1.316977577486093</v>
+        <v>-2.065855672680361</v>
       </c>
       <c r="G18">
-        <v>-5.522046692992519</v>
+        <v>-7.715724835675458</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>6.586563114222616</v>
       </c>
       <c r="E19">
-        <v>-34.13370156569317</v>
+        <v>-32.75703660785225</v>
       </c>
       <c r="F19">
-        <v>-1.33170346480566</v>
+        <v>-1.807616276694629</v>
       </c>
       <c r="G19">
-        <v>-5.097808529170384</v>
+        <v>-7.336681271470084</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>7.232459656992005</v>
       </c>
       <c r="E20">
-        <v>-35.58731929956618</v>
+        <v>-33.35372432567905</v>
       </c>
       <c r="F20">
-        <v>-0.9690367605534114</v>
+        <v>-1.54354268909098</v>
       </c>
       <c r="G20">
-        <v>-4.402987574436085</v>
+        <v>-6.166182652234944</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>7.746140062825595</v>
       </c>
       <c r="E21">
-        <v>-33.47810885164633</v>
+        <v>-34.50617817014909</v>
       </c>
       <c r="F21">
-        <v>-0.9876054442545651</v>
+        <v>-1.388232084740101</v>
       </c>
       <c r="G21">
-        <v>-3.498607372862305</v>
+        <v>-6.041148872277347</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>8.106550057027441</v>
       </c>
       <c r="E22">
-        <v>-36.55513590477398</v>
+        <v>-35.15664582142109</v>
       </c>
       <c r="F22">
-        <v>-1.192846722176587</v>
+        <v>-0.9690524995340646</v>
       </c>
       <c r="G22">
-        <v>-3.137677154630075</v>
+        <v>-5.451441716270452</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>8.306031474909958</v>
       </c>
       <c r="E23">
-        <v>-34.71554778285068</v>
+        <v>-35.32240048539499</v>
       </c>
       <c r="F23">
-        <v>-0.9145881711673999</v>
+        <v>-0.7920585500475055</v>
       </c>
       <c r="G23">
-        <v>-2.81967279896493</v>
+        <v>-4.964919018738127</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>8.347411096827516</v>
       </c>
       <c r="E24">
-        <v>-35.90252727306403</v>
+        <v>-37.44986429708745</v>
       </c>
       <c r="F24">
-        <v>-0.8030195075213485</v>
+        <v>-0.4942803495587503</v>
       </c>
       <c r="G24">
-        <v>-2.30096223136877</v>
+        <v>-4.55650718862732</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>8.248681363747155</v>
       </c>
       <c r="E25">
-        <v>-35.48514614776406</v>
+        <v>-37.80729381691352</v>
       </c>
       <c r="F25">
-        <v>-0.7403858198282751</v>
+        <v>-0.8415957491023187</v>
       </c>
       <c r="G25">
-        <v>-1.891033558650526</v>
+        <v>-4.222115189163756</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>8.030758107114959</v>
       </c>
       <c r="E26">
-        <v>-34.95367215415973</v>
+        <v>-37.36938129142926</v>
       </c>
       <c r="F26">
-        <v>-0.5409737633197529</v>
+        <v>-0.6086472382914585</v>
       </c>
       <c r="G26">
-        <v>-1.303057326307538</v>
+        <v>-4.675189026994738</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>7.717931064379103</v>
       </c>
       <c r="E27">
-        <v>-38.3572080688001</v>
+        <v>-36.61329955277254</v>
       </c>
       <c r="F27">
-        <v>-0.4548641434313415</v>
+        <v>-0.6997585405579734</v>
       </c>
       <c r="G27">
-        <v>-3.517610982741019</v>
+        <v>-4.410704935447415</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>7.335093253699867</v>
       </c>
       <c r="E28">
-        <v>-37.04607663245365</v>
+        <v>-38.25781549197996</v>
       </c>
       <c r="F28">
-        <v>-0.8183012293681938</v>
+        <v>-0.9665599420190409</v>
       </c>
       <c r="G28">
-        <v>-2.844584523853333</v>
+        <v>-4.357309987069967</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>6.899560210586415</v>
       </c>
       <c r="E29">
-        <v>-37.31205036230133</v>
+        <v>-38.43422106639639</v>
       </c>
       <c r="F29">
-        <v>-0.921475217754275</v>
+        <v>-0.8082001172584566</v>
       </c>
       <c r="G29">
-        <v>-2.51405903712921</v>
+        <v>-4.870182929760398</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>6.430396125468169</v>
       </c>
       <c r="E30">
-        <v>-37.52862164344018</v>
+        <v>-37.99381453751158</v>
       </c>
       <c r="F30">
-        <v>-0.9300430218014303</v>
+        <v>-1.043608879255631</v>
       </c>
       <c r="G30">
-        <v>-3.189769341456559</v>
+        <v>-4.191968921370171</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>5.940593414397264</v>
       </c>
       <c r="E31">
-        <v>-37.67321569571408</v>
+        <v>-36.98550412188668</v>
       </c>
       <c r="F31">
-        <v>-0.9710496933422142</v>
+        <v>-1.08001562660867</v>
       </c>
       <c r="G31">
-        <v>-2.53863658670995</v>
+        <v>-4.608129441427402</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>5.443178646044711</v>
       </c>
       <c r="E32">
-        <v>-37.07743753116743</v>
+        <v>-37.62957167450713</v>
       </c>
       <c r="F32">
-        <v>-1.256959874051061</v>
+        <v>-1.161751466610299</v>
       </c>
       <c r="G32">
-        <v>-4.102582248059635</v>
+        <v>-4.987747369442821</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>4.952795208978126</v>
       </c>
       <c r="E33">
-        <v>-33.49916978627454</v>
+        <v>-37.18777589643415</v>
       </c>
       <c r="F33">
-        <v>-0.3143970545712265</v>
+        <v>-1.136784473089923</v>
       </c>
       <c r="G33">
-        <v>-3.488281878004452</v>
+        <v>-4.727531845301969</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>4.478345323797023</v>
       </c>
       <c r="E34">
-        <v>-36.5335267462509</v>
+        <v>-36.15886347603245</v>
       </c>
       <c r="F34">
-        <v>-0.543241833268618</v>
+        <v>-0.9859694186340361</v>
       </c>
       <c r="G34">
-        <v>-3.856297657056963</v>
+        <v>-5.134528651844392</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>4.037566800126703</v>
       </c>
       <c r="E35">
-        <v>-34.64573645369164</v>
+        <v>-35.55127357847798</v>
       </c>
       <c r="F35">
-        <v>-1.021677023899112</v>
+        <v>-1.249599001309784</v>
       </c>
       <c r="G35">
-        <v>-4.636719705444684</v>
+        <v>-5.13105114004903</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>3.639993998286594</v>
       </c>
       <c r="E36">
-        <v>-34.78608177078025</v>
+        <v>-35.50267892937183</v>
       </c>
       <c r="F36">
-        <v>-0.6838969615291683</v>
+        <v>-1.565771099977702</v>
       </c>
       <c r="G36">
-        <v>-3.746074631164751</v>
+        <v>-5.559262857138839</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>3.302566541650641</v>
       </c>
       <c r="E37">
-        <v>-33.62189510431756</v>
+        <v>-34.62095631832205</v>
       </c>
       <c r="F37">
-        <v>-1.172902948586787</v>
+        <v>-1.504443747678844</v>
       </c>
       <c r="G37">
-        <v>-2.602941836733661</v>
+        <v>-5.672258493786813</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>3.037188720669117</v>
       </c>
       <c r="E38">
-        <v>-32.60133894510142</v>
+        <v>-33.33638882160921</v>
       </c>
       <c r="F38">
-        <v>-0.9267154699443847</v>
+        <v>-1.590673480840661</v>
       </c>
       <c r="G38">
-        <v>-4.104783105749943</v>
+        <v>-5.120065126809624</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>2.859029310018947</v>
       </c>
       <c r="E39">
-        <v>-34.9855085955702</v>
+        <v>-33.72256271701442</v>
       </c>
       <c r="F39">
-        <v>-0.4467908747236575</v>
+        <v>-1.609666288652048</v>
       </c>
       <c r="G39">
-        <v>-4.816398980438874</v>
+        <v>-5.642681368314091</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>2.780876133220008</v>
       </c>
       <c r="E40">
-        <v>-32.42032745932575</v>
+        <v>-32.6212245209247</v>
       </c>
       <c r="F40">
-        <v>-1.059274135209973</v>
+        <v>-1.614355676519296</v>
       </c>
       <c r="G40">
-        <v>-3.94643622480974</v>
+        <v>-5.156586832894709</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>2.815899367379882</v>
       </c>
       <c r="E41">
-        <v>-30.69714346780909</v>
+        <v>-33.66754097338309</v>
       </c>
       <c r="F41">
-        <v>-0.734787712920156</v>
+        <v>-1.667746440731933</v>
       </c>
       <c r="G41">
-        <v>-4.426888941167727</v>
+        <v>-5.75259110485537</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>2.974357669598736</v>
       </c>
       <c r="E42">
-        <v>-30.71759180376689</v>
+        <v>-32.05741154733958</v>
       </c>
       <c r="F42">
-        <v>-0.7216373804007139</v>
+        <v>-1.365455294632726</v>
       </c>
       <c r="G42">
-        <v>-3.514371048703447</v>
+        <v>-5.751426712767732</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>3.2571883142441</v>
       </c>
       <c r="E43">
-        <v>-29.31127914688368</v>
+        <v>-30.84031712180991</v>
       </c>
       <c r="F43">
-        <v>-0.8800079739375345</v>
+        <v>-1.531389710924509</v>
       </c>
       <c r="G43">
-        <v>-2.462267085930704</v>
+        <v>-5.999251643079162</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>3.663719210575286</v>
       </c>
       <c r="E44">
-        <v>-29.52452162914568</v>
+        <v>-30.32071300617193</v>
       </c>
       <c r="F44">
-        <v>-0.718376926303295</v>
+        <v>-1.22865704499961</v>
       </c>
       <c r="G44">
-        <v>-3.105967050826413</v>
+        <v>-5.46192124505918</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>4.177894284888694</v>
       </c>
       <c r="E45">
-        <v>-29.58625496227793</v>
+        <v>-29.67099708614973</v>
       </c>
       <c r="F45">
-        <v>-0.389322057787039</v>
+        <v>-1.362315782176116</v>
       </c>
       <c r="G45">
-        <v>-3.934630437768726</v>
+        <v>-5.86346942763995</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>4.785797681640136</v>
       </c>
       <c r="E46">
-        <v>-28.88007198108336</v>
+        <v>-29.39514494316594</v>
       </c>
       <c r="F46">
-        <v>0.1544398429630293</v>
+        <v>-1.210023748641038</v>
       </c>
       <c r="G46">
-        <v>-4.531616349695645</v>
+        <v>-6.271951747854717</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>5.457005818595186</v>
       </c>
       <c r="E47">
-        <v>-26.57472820495416</v>
+        <v>-27.9022025278638</v>
       </c>
       <c r="F47">
-        <v>-1.036627398784837</v>
+        <v>-1.392455101759573</v>
       </c>
       <c r="G47">
-        <v>-3.714395856296183</v>
+        <v>-6.288292398250495</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>6.167256380397123</v>
       </c>
       <c r="E48">
-        <v>-26.85016918001678</v>
+        <v>-27.94164142260437</v>
       </c>
       <c r="F48">
-        <v>0.06328960742858288</v>
+        <v>-0.91908289269499</v>
       </c>
       <c r="G48">
-        <v>-4.381869261438569</v>
+        <v>-6.461844255689342</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>6.88596372250669</v>
       </c>
       <c r="E49">
-        <v>-25.84699836340637</v>
+        <v>-26.99212594309942</v>
       </c>
       <c r="F49">
-        <v>-0.3877746674786095</v>
+        <v>-1.061919112327112</v>
       </c>
       <c r="G49">
-        <v>-4.151933153065449</v>
+        <v>-6.248167864629675</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>7.582351273771073</v>
       </c>
       <c r="E50">
-        <v>-25.04267915181743</v>
+        <v>-27.1778658599684</v>
       </c>
       <c r="F50">
-        <v>-0.5306233126217731</v>
+        <v>-1.319998633404103</v>
       </c>
       <c r="G50">
-        <v>-5.136849603785892</v>
+        <v>-7.060869159141921</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>8.231474580772085</v>
       </c>
       <c r="E51">
-        <v>-24.4904972465475</v>
+        <v>-24.98645713011322</v>
       </c>
       <c r="F51">
-        <v>-0.9571546585276554</v>
+        <v>-1.051552094281076</v>
       </c>
       <c r="G51">
-        <v>-5.205747153545372</v>
+        <v>-7.049311392837063</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>8.802084675098662</v>
       </c>
       <c r="E52">
-        <v>-24.21649743581458</v>
+        <v>-25.33131487925904</v>
       </c>
       <c r="F52">
-        <v>-1.27585576287632</v>
+        <v>-0.7861713429158094</v>
       </c>
       <c r="G52">
-        <v>-5.606031735744042</v>
+        <v>-7.170679687388737</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>9.274056500104734</v>
       </c>
       <c r="E53">
-        <v>-23.6612961459115</v>
+        <v>-24.63843463393789</v>
       </c>
       <c r="F53">
-        <v>-1.049562355779551</v>
+        <v>-1.202367977104365</v>
       </c>
       <c r="G53">
-        <v>-5.30156409078382</v>
+        <v>-6.917970053947335</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>9.6241428443698</v>
       </c>
       <c r="E54">
-        <v>-23.96463008823168</v>
+        <v>-23.70306499220531</v>
       </c>
       <c r="F54">
-        <v>-1.306282525948549</v>
+        <v>-0.7713377678338786</v>
       </c>
       <c r="G54">
-        <v>-6.083380276783195</v>
+        <v>-7.232898952484149</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>9.838748590884906</v>
       </c>
       <c r="E55">
-        <v>-22.5756757780806</v>
+        <v>-22.77837741000018</v>
       </c>
       <c r="F55">
-        <v>-1.018911933508567</v>
+        <v>-1.398783828716961</v>
       </c>
       <c r="G55">
-        <v>-5.702415204558763</v>
+        <v>-7.599826051042165</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>9.909023482368433</v>
       </c>
       <c r="E56">
-        <v>-20.71902834064057</v>
+        <v>-21.6769706859236</v>
       </c>
       <c r="F56">
-        <v>-0.7301886170998132</v>
+        <v>-1.300529514336106</v>
       </c>
       <c r="G56">
-        <v>-4.453262683027154</v>
+        <v>-7.760495189296164</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>9.830318730879172</v>
       </c>
       <c r="E57">
-        <v>-21.12619256608146</v>
+        <v>-21.45266404869226</v>
       </c>
       <c r="F57">
-        <v>-1.485739211723631</v>
+        <v>-1.480409495854019</v>
       </c>
       <c r="G57">
-        <v>-5.757791708080867</v>
+        <v>-7.979235119490295</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>9.610330153808032</v>
       </c>
       <c r="E58">
-        <v>-19.41580877186792</v>
+        <v>-21.13780079173436</v>
       </c>
       <c r="F58">
-        <v>-1.377514667282681</v>
+        <v>-1.760589859237701</v>
       </c>
       <c r="G58">
-        <v>-6.547706423801876</v>
+        <v>-8.098488710923167</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>9.261365081006506</v>
       </c>
       <c r="E59">
-        <v>-19.29947316944815</v>
+        <v>-20.8811572511279</v>
       </c>
       <c r="F59">
-        <v>-0.7964629795281905</v>
+        <v>-1.526178451593497</v>
       </c>
       <c r="G59">
-        <v>-6.544677960076185</v>
+        <v>-8.727991446732403</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>8.803678679235253</v>
       </c>
       <c r="E60">
-        <v>-19.63890682460374</v>
+        <v>-20.43764412017211</v>
       </c>
       <c r="F60">
-        <v>-2.122207850358006</v>
+        <v>-1.526748368366623</v>
       </c>
       <c r="G60">
-        <v>-5.537969624253719</v>
+        <v>-9.190225081961305</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>8.267927104509793</v>
       </c>
       <c r="E61">
-        <v>-18.22166499211925</v>
+        <v>-19.52389609659659</v>
       </c>
       <c r="F61">
-        <v>-1.1001457828641</v>
+        <v>-2.100691007070289</v>
       </c>
       <c r="G61">
-        <v>-6.104368052551155</v>
+        <v>-9.123489228723267</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>7.68361863607164</v>
       </c>
       <c r="E62">
-        <v>-18.63402903813882</v>
+        <v>-18.89445200105087</v>
       </c>
       <c r="F62">
-        <v>-1.758539649915773</v>
+        <v>-2.108679782302887</v>
       </c>
       <c r="G62">
-        <v>-5.853368456816933</v>
+        <v>-9.55744980540271</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>7.089397733849022</v>
       </c>
       <c r="E63">
-        <v>-16.68324906602156</v>
+        <v>-17.55985492071914</v>
       </c>
       <c r="F63">
-        <v>-1.437616864192799</v>
+        <v>-2.289442803472184</v>
       </c>
       <c r="G63">
-        <v>-7.205585342571922</v>
+        <v>-9.8147164935279</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>6.516348605138837</v>
       </c>
       <c r="E64">
-        <v>-18.07940089139857</v>
+        <v>-17.89599923250547</v>
       </c>
       <c r="F64">
-        <v>-1.654929111908416</v>
+        <v>-2.459371607380267</v>
       </c>
       <c r="G64">
-        <v>-7.241660611331925</v>
+        <v>-9.843711422956803</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>5.998171892983768</v>
       </c>
       <c r="E65">
-        <v>-17.06805240168957</v>
+        <v>-17.30225614150798</v>
       </c>
       <c r="F65">
-        <v>-1.937272342580808</v>
+        <v>-2.763038671735523</v>
       </c>
       <c r="G65">
-        <v>-7.107640648491715</v>
+        <v>-9.627646200596269</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>5.561234140623448</v>
       </c>
       <c r="E66">
-        <v>-17.02171086972713</v>
+        <v>-16.88800653754693</v>
       </c>
       <c r="F66">
-        <v>-2.64397742493115</v>
+        <v>-2.517413654559622</v>
       </c>
       <c r="G66">
-        <v>-6.869699997202241</v>
+        <v>-9.839346258000463</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>5.223604333560163</v>
       </c>
       <c r="E67">
-        <v>-17.01909849980382</v>
+        <v>-17.10764911846049</v>
       </c>
       <c r="F67">
-        <v>-2.174028858342338</v>
+        <v>-3.093302956659866</v>
       </c>
       <c r="G67">
-        <v>-6.467922069097454</v>
+        <v>-10.26586360185064</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>5.003417094719702</v>
       </c>
       <c r="E68">
-        <v>-15.60398726472896</v>
+        <v>-16.5011930475977</v>
       </c>
       <c r="F68">
-        <v>-2.769705372593254</v>
+        <v>-3.165905217678229</v>
       </c>
       <c r="G68">
-        <v>-7.426005286910434</v>
+        <v>-10.25104240480689</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>4.904978255281231</v>
       </c>
       <c r="E69">
-        <v>-17.31910987306413</v>
+        <v>-15.79611897382686</v>
       </c>
       <c r="F69">
-        <v>-2.258891785289535</v>
+        <v>-3.423941663650275</v>
       </c>
       <c r="G69">
-        <v>-7.207081299222629</v>
+        <v>-9.976754967319936</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>4.933023521853235</v>
       </c>
       <c r="E70">
-        <v>-16.15879815276751</v>
+        <v>-15.28950195000162</v>
       </c>
       <c r="F70">
-        <v>-2.346000416265723</v>
+        <v>-3.509188124704969</v>
       </c>
       <c r="G70">
-        <v>-7.423639952310886</v>
+        <v>-9.523917401874451</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>5.077429954147802</v>
       </c>
       <c r="E71">
-        <v>-15.31173409022343</v>
+        <v>-15.8072163544868</v>
       </c>
       <c r="F71">
-        <v>-2.621862500378612</v>
+        <v>-3.706048809612869</v>
       </c>
       <c r="G71">
-        <v>-6.769645821492416</v>
+        <v>-9.728821691107976</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>5.329661574908441</v>
       </c>
       <c r="E72">
-        <v>-15.78951121460905</v>
+        <v>-16.58570259163531</v>
       </c>
       <c r="F72">
-        <v>-3.514719133853462</v>
+        <v>-3.670749589477374</v>
       </c>
       <c r="G72">
-        <v>-7.074969790678524</v>
+        <v>-8.934238964058057</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>5.669658856323748</v>
       </c>
       <c r="E73">
-        <v>-16.04997570963435</v>
+        <v>-16.28359799986728</v>
       </c>
       <c r="F73">
-        <v>-2.869393590948354</v>
+        <v>-3.84813618511286</v>
       </c>
       <c r="G73">
-        <v>-6.003901379195934</v>
+        <v>-9.266725119970108</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>6.080087252123594</v>
       </c>
       <c r="E74">
-        <v>-17.37730051693631</v>
+        <v>-16.69256887223447</v>
       </c>
       <c r="F74">
-        <v>-3.399418675057798</v>
+        <v>-4.013982794459946</v>
       </c>
       <c r="G74">
-        <v>-6.699604765602029</v>
+        <v>-8.306194329102958</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>6.539681631304426</v>
       </c>
       <c r="E75">
-        <v>-17.77440151133714</v>
+        <v>-16.48807305302256</v>
       </c>
       <c r="F75">
-        <v>-3.142630578761771</v>
+        <v>-3.891869013776257</v>
       </c>
       <c r="G75">
-        <v>-5.972311369643463</v>
+        <v>-8.517259975571513</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>7.02732566299507</v>
       </c>
       <c r="E76">
-        <v>-15.68875015465739</v>
+        <v>-16.4339982415733</v>
       </c>
       <c r="F76">
-        <v>-3.20142809701248</v>
+        <v>-4.559547222678506</v>
       </c>
       <c r="G76">
-        <v>-5.951357533555188</v>
+        <v>-7.351053420444162</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>7.528053097582404</v>
       </c>
       <c r="E77">
-        <v>-16.70507834474486</v>
+        <v>-17.43593140120891</v>
       </c>
       <c r="F77">
-        <v>-3.508492296086618</v>
+        <v>-4.436325086409871</v>
       </c>
       <c r="G77">
-        <v>-6.674546839016524</v>
+        <v>-7.247030912955845</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>8.023500846665332</v>
       </c>
       <c r="E78">
-        <v>-18.72157873286621</v>
+        <v>-17.64221725450182</v>
       </c>
       <c r="F78">
-        <v>-3.363466701408897</v>
+        <v>-4.348818010712937</v>
       </c>
       <c r="G78">
-        <v>-4.08960162595262</v>
+        <v>-7.187947152114361</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>8.511691433101399</v>
       </c>
       <c r="E79">
-        <v>-18.80618795397562</v>
+        <v>-17.50580918174915</v>
       </c>
       <c r="F79">
-        <v>-3.700627144961546</v>
+        <v>-3.938696623056513</v>
       </c>
       <c r="G79">
-        <v>-4.859016775144207</v>
+        <v>-6.914419441303421</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>8.982118348424887</v>
       </c>
       <c r="E80">
-        <v>-17.48754335834255</v>
+        <v>-19.10876601183467</v>
       </c>
       <c r="F80">
-        <v>-2.701587064326245</v>
+        <v>-4.925416395309978</v>
       </c>
       <c r="G80">
-        <v>-5.137718981734732</v>
+        <v>-6.432977252745403</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>9.442317856450426</v>
       </c>
       <c r="E81">
-        <v>-19.93674191512984</v>
+        <v>-18.76728897670727</v>
       </c>
       <c r="F81">
-        <v>-3.067558126148261</v>
+        <v>-4.314595668201081</v>
       </c>
       <c r="G81">
-        <v>-3.329308418362382</v>
+        <v>-6.031836346320846</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>9.893889504166562</v>
       </c>
       <c r="E82">
-        <v>-19.68744125214569</v>
+        <v>-19.40542989676718</v>
       </c>
       <c r="F82">
-        <v>-3.298445658860956</v>
+        <v>-4.503140372752276</v>
       </c>
       <c r="G82">
-        <v>-3.742516186287064</v>
+        <v>-5.935069098051232</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>10.34220337774271</v>
       </c>
       <c r="E83">
-        <v>-21.49351503528327</v>
+        <v>-20.55581128878613</v>
       </c>
       <c r="F83">
-        <v>-3.457561783060296</v>
+        <v>-4.322161147690849</v>
       </c>
       <c r="G83">
-        <v>-3.489414941156995</v>
+        <v>-5.145780961032091</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>10.79551881309336</v>
       </c>
       <c r="E84">
-        <v>-20.41640875066826</v>
+        <v>-21.30240501617129</v>
       </c>
       <c r="F84">
-        <v>-3.875362964908074</v>
+        <v>-4.592056501401372</v>
       </c>
       <c r="G84">
-        <v>-3.299945373946131</v>
+        <v>-4.772003268666992</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>11.2496542052064</v>
       </c>
       <c r="E85">
-        <v>-24.13739952613323</v>
+        <v>-22.39065851998214</v>
       </c>
       <c r="F85">
-        <v>-3.348455855702767</v>
+        <v>-4.760419690918164</v>
       </c>
       <c r="G85">
-        <v>-3.375962424205576</v>
+        <v>-5.130688246550864</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>11.70853383204533</v>
       </c>
       <c r="E86">
-        <v>-23.59465371699331</v>
+        <v>-23.28155557484846</v>
       </c>
       <c r="F86">
-        <v>-2.66652475726795</v>
+        <v>-4.639395213369157</v>
       </c>
       <c r="G86">
-        <v>-2.640573109269968</v>
+        <v>-4.778104578776424</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>12.15744465574983</v>
       </c>
       <c r="E87">
-        <v>-25.23199498363709</v>
+        <v>-24.71874112811478</v>
       </c>
       <c r="F87">
-        <v>-4.005686694920909</v>
+        <v>-4.427230440694536</v>
       </c>
       <c r="G87">
-        <v>-3.089041593642226</v>
+        <v>-4.53791085490482</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>12.58835402319613</v>
       </c>
       <c r="E88">
-        <v>-25.71047815394793</v>
+        <v>-25.63631841253179</v>
       </c>
       <c r="F88">
-        <v>-4.037255776641598</v>
+        <v>-4.625581358560072</v>
       </c>
       <c r="G88">
-        <v>-2.634531846286132</v>
+        <v>-4.252170080896652</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>12.98482196353258</v>
       </c>
       <c r="E89">
-        <v>-26.58595848837649</v>
+        <v>-27.4372256007813</v>
       </c>
       <c r="F89">
-        <v>-4.36201887364395</v>
+        <v>-4.621722823197832</v>
       </c>
       <c r="G89">
-        <v>-3.504836609456701</v>
+        <v>-4.48092613271459</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>13.32352633163454</v>
       </c>
       <c r="E90">
-        <v>-28.80698169158336</v>
+        <v>-28.65321527209857</v>
       </c>
       <c r="F90">
-        <v>-4.241545260417804</v>
+        <v>-4.671381792260856</v>
       </c>
       <c r="G90">
-        <v>-3.165559906863165</v>
+        <v>-4.303304124458197</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>13.58681689569287</v>
       </c>
       <c r="E91">
-        <v>-31.52169504836694</v>
+        <v>-30.09278476866534</v>
       </c>
       <c r="F91">
-        <v>-4.171823232858975</v>
+        <v>-4.414413111871019</v>
       </c>
       <c r="G91">
-        <v>-2.178899478755859</v>
+        <v>-4.6505227120979</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>13.7493398268579</v>
       </c>
       <c r="E92">
-        <v>-31.75769505208333</v>
+        <v>-31.57458619458863</v>
       </c>
       <c r="F92">
-        <v>-3.727687422908798</v>
+        <v>-4.818036785619883</v>
       </c>
       <c r="G92">
-        <v>-3.394866825789828</v>
+        <v>-4.73522570961198</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>13.79279968011628</v>
       </c>
       <c r="E93">
-        <v>-31.88183038537113</v>
+        <v>-33.72132921325095</v>
       </c>
       <c r="F93">
-        <v>-3.963355463903049</v>
+        <v>-4.489115284255478</v>
       </c>
       <c r="G93">
-        <v>-4.271740222351638</v>
+        <v>-5.226416418473216</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>13.69933304088608</v>
       </c>
       <c r="E94">
-        <v>-37.01031748294687</v>
+        <v>-33.91495607842577</v>
       </c>
       <c r="F94">
-        <v>-3.998977747325636</v>
+        <v>-4.520533603108857</v>
       </c>
       <c r="G94">
-        <v>-3.071737578492327</v>
+        <v>-5.079055550772417</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>13.4584109921072</v>
       </c>
       <c r="E95">
-        <v>-37.34798809989508</v>
+        <v>-37.63633310254394</v>
       </c>
       <c r="F95">
-        <v>-4.156450390597822</v>
+        <v>-4.317320168588889</v>
       </c>
       <c r="G95">
-        <v>-4.921927887556264</v>
+        <v>-5.286126758016567</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>13.0585533678595</v>
       </c>
       <c r="E96">
-        <v>-40.15603657478152</v>
+        <v>-39.43689765085915</v>
       </c>
       <c r="F96">
-        <v>-3.24586006776384</v>
+        <v>-4.465095114676501</v>
       </c>
       <c r="G96">
-        <v>-4.150147403765128</v>
+        <v>-5.665011066801883</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>12.50987942479135</v>
       </c>
       <c r="E97">
-        <v>-41.84920323144799</v>
+        <v>-41.35697085504629</v>
       </c>
       <c r="F97">
-        <v>-3.216182977191145</v>
+        <v>-4.056381951604836</v>
       </c>
       <c r="G97">
-        <v>-4.35637795125094</v>
+        <v>-6.694406773121123</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>11.79314201320859</v>
       </c>
       <c r="E98">
-        <v>-42.06612130573246</v>
+        <v>-42.92568445775861</v>
       </c>
       <c r="F98">
-        <v>-3.24692534824384</v>
+        <v>-4.227409170689031</v>
       </c>
       <c r="G98">
-        <v>-5.604658484089117</v>
+        <v>-6.698273285860561</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>10.96070211446023</v>
       </c>
       <c r="E99">
-        <v>-46.41266357942894</v>
+        <v>-45.88508322144163</v>
       </c>
       <c r="F99">
-        <v>-3.643870723991335</v>
+        <v>-3.990156462853224</v>
       </c>
       <c r="G99">
-        <v>-5.873296270280901</v>
+        <v>-7.256299056254297</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>9.957730529067602</v>
       </c>
       <c r="E100">
-        <v>-45.9264253252718</v>
+        <v>-47.08754069195978</v>
       </c>
       <c r="F100">
-        <v>-2.667353953038152</v>
+        <v>-3.549727597030575</v>
       </c>
       <c r="G100">
-        <v>-5.451060547560149</v>
+        <v>-8.078319403584523</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>8.917720478838625</v>
       </c>
       <c r="E101">
-        <v>-47.20820809379135</v>
+        <v>-50.02999539174033</v>
       </c>
       <c r="F101">
-        <v>-2.267576389140486</v>
+        <v>-3.555562617015894</v>
       </c>
       <c r="G101">
-        <v>-5.899374998001531</v>
+        <v>-8.114033084218656</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>7.670557824780086</v>
       </c>
       <c r="E102">
-        <v>-52.40903374961729</v>
+        <v>-52.14128867513957</v>
       </c>
       <c r="F102">
-        <v>-3.033584293857245</v>
+        <v>-3.219916429075563</v>
       </c>
       <c r="G102">
-        <v>-7.343881705052374</v>
+        <v>-8.142952302054418</v>
       </c>
     </row>
   </sheetData>
